--- a/KatalonData/BWPBootstrapData/NormalizedSharedData.xlsx
+++ b/KatalonData/BWPBootstrapData/NormalizedSharedData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\BWPBootstrapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14889E1-47C8-4DF9-88E6-6AC448396097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2498DAC0-9F2D-4397-9C16-9EE901CEF382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BCCB990F-B3AB-4CDA-A16C-818C7712AEED}"/>
+    <workbookView xWindow="1500" yWindow="1500" windowWidth="17280" windowHeight="9000" activeTab="1" xr2:uid="{BCCB990F-B3AB-4CDA-A16C-818C7712AEED}"/>
   </bookViews>
   <sheets>
     <sheet name="NameData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="98">
   <si>
     <t>ID</t>
   </si>
@@ -321,6 +321,9 @@
   </si>
   <si>
     <t>Waters</t>
+  </si>
+  <si>
+    <t>2026</t>
   </si>
 </sst>
 </file>
@@ -1004,6 +1007,9 @@
       <c r="E8" s="1" t="s">
         <v>89</v>
       </c>
+      <c r="F8" s="1" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
